--- a/generated/excel/activitypods-ontology.xlsx
+++ b/generated/excel/activitypods-ontology.xlsx
@@ -15,6 +15,8 @@
     <sheet name="Activity" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Collection" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="OrderedCollection" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Authorization" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="ActivityGrant" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -450,6 +452,19 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -601,4 +616,17 @@
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>